--- a/Research Logs/Matt/Matt Baker - Week 4 Research Log.xlsx
+++ b/Research Logs/Matt/Matt Baker - Week 4 Research Log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\Weltec\IT 7510 Capstone\Week 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\Weltec\IT 7510 Capstone\Week 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA64DC6-E57D-4A19-9BF4-2C4C6D1CB9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C505BA06-6501-4143-ABEA-D918B249A916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4035" yWindow="4200" windowWidth="28800" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="2910" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>Date</t>
   </si>
@@ -141,6 +141,43 @@
   </si>
   <si>
     <t>Unique investigative platform with its own AI agent that conducts file carving, metadata extraction, automatic hashing, and creates a timeline of events based on the forensic evidence. Includes unique features that may reveal otherwise undetectable insights such as AI generated content detection, automatic false-context/false-claim detection based on existing environmental &amp; open source information.</t>
+  </si>
+  <si>
+    <t>Find metrics and processes by which tool testing has been undertaken by other organizations</t>
+  </si>
+  <si>
+    <t>NIST'S Computer Forensics Tools and Techniques Catalog:
+https://toolcatalog.nist.gov/search/index.php</t>
+  </si>
+  <si>
+    <t>I was specifically looking for tools with available test reports, and read some of that documentation</t>
+  </si>
+  <si>
+    <t>https://www.ojp.gov/pdffiles1/nij/238993.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The U.S DOJ created a report on the mobile digital forensics tool "Cellebrite Physical Analyzer" I read parts of this report, it was particularly informative to see how NIST's CTFF methodology is applied by a government department, gave me a good idea of how we can design our test cases/testing environment and inspired the next stage of my research. </t>
+  </si>
+  <si>
+    <t>https://www.dhs.gov/sites/default/files/2025-08/25_0805_st_test_
+results_for_mobile_device_acquisition_tool_belkasoft_evidence_center_x_v2.7.19314.pdf</t>
+  </si>
+  <si>
+    <t>The U.S DHS created a report on Belkasoft Evidence 
+Center X which I researched previously, the current version supports natural language data analysis, however the report did not include "agent-based acquisitions". The tables for data objects and data elements are a good inspiration for how to design our test documentation.</t>
+  </si>
+  <si>
+    <t>Listening</t>
+  </si>
+  <si>
+    <t>Find anecdotal perspectives on the state and usefulness of AI in modern digital forensics</t>
+  </si>
+  <si>
+    <t>The AI Investigative Framework Interview with Heather Barnhart
+https://open.spotify.com/episode/6Rljo1PtpUiz0N779Muyp0</t>
+  </si>
+  <si>
+    <t>Listened to a podcast where forensic examiner with 24 year's experience Heather Barngarter goes over the philosophy behind a framework for determining where and where not AI has a place in DFIR, the prevailing sentiment is that it does not belong in digital forensics, but could be useful in incident response. AI can be used to "find a thread to pull" or to discover something in a case previously unseen, but the risks are too great due to unvalidatable results, lack of accountability when something goes wrong, the inability to resolve insights that are not there and much more, it is a tool, a tool does not determine guilt, the forensic examiner and investigator does.</t>
   </si>
 </sst>
 </file>
@@ -499,12 +536,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G15"/>
+  <dimension ref="B2:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" style="3" customWidth="1"/>
     <col min="3" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="86.28515625" customWidth="1"/>
+    <col min="5" max="5" width="91.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="54.5703125" customWidth="1"/>
     <col min="7" max="7" width="131" customWidth="1"/>
     <col min="8" max="8" width="33.42578125" customWidth="1"/>
@@ -516,7 +553,7 @@
       </c>
       <c r="D2" s="5">
         <f>ROUNDDOWN(SUM(C6:C500)/60,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -528,7 +565,7 @@
       </c>
       <c r="D3" s="5">
         <f>ROUND(MOD(SUM(C6:C500),60),0)</f>
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -651,18 +688,99 @@
         <v>25</v>
       </c>
     </row>
+    <row r="13" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
+        <v>46239</v>
+      </c>
+      <c r="C13">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F14" s="1"/>
+      <c r="B14" s="3">
+        <v>46239</v>
+      </c>
+      <c r="C14">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F15" s="1"/>
+    <row r="15" spans="2:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B16" s="3">
+        <v>46239</v>
+      </c>
+      <c r="C16">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="195" x14ac:dyDescent="0.25">
+      <c r="B17" s="3">
+        <v>46239</v>
+      </c>
+      <c r="C17">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F18" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G8" r:id="rId1" xr:uid="{2D576095-DD33-41E2-AE3D-624BFE4181D0}"/>
     <hyperlink ref="G9" r:id="rId2" xr:uid="{4C5458C7-3251-4B50-B993-29D9C5092585}"/>
     <hyperlink ref="G10" r:id="rId3" xr:uid="{37D06B73-17A9-4592-98F1-C038CB44CDA2}"/>
+    <hyperlink ref="G16" r:id="rId4" xr:uid="{AAFD389F-5339-488C-8F44-9A3F039DCFDD}"/>
+    <hyperlink ref="G17" r:id="rId5" display="https://open.spotify.com/episode/6Rljo1PtpUiz0N779Muyp0" xr:uid="{174DB1DB-772B-43EC-AFB0-0428427A70E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Research Logs/Matt/Matt Baker - Week 4 Research Log.xlsx
+++ b/Research Logs/Matt/Matt Baker - Week 4 Research Log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\Weltec\IT 7510 Capstone\Week 4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\BHB-Capstone\Research Logs\Matt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C505BA06-6501-4143-ABEA-D918B249A916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9108FB-8F29-4FB8-900A-DDA0996028AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2910" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>Date</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>Listened to a podcast where forensic examiner with 24 year's experience Heather Barngarter goes over the philosophy behind a framework for determining where and where not AI has a place in DFIR, the prevailing sentiment is that it does not belong in digital forensics, but could be useful in incident response. AI can be used to "find a thread to pull" or to discover something in a case previously unseen, but the risks are too great due to unvalidatable results, lack of accountability when something goes wrong, the inability to resolve insights that are not there and much more, it is a tool, a tool does not determine guilt, the forensic examiner and investigator does.</t>
+  </si>
+  <si>
+    <t>WEEK 4</t>
   </si>
 </sst>
 </file>
@@ -536,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G18"/>
+  <dimension ref="B2:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" style="3" customWidth="1"/>
@@ -552,7 +555,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="5">
-        <f>ROUNDDOWN(SUM(C6:C500)/60,0)</f>
+        <f>ROUNDDOWN(SUM(C6:C499)/60,0)</f>
         <v>4</v>
       </c>
       <c r="E2" t="s">
@@ -564,7 +567,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="5">
-        <f>ROUND(MOD(SUM(C6:C500),60),0)</f>
+        <f>ROUND(MOD(SUM(C6:C499),60),0)</f>
         <v>45</v>
       </c>
     </row>
@@ -688,6 +691,11 @@
         <v>25</v>
       </c>
     </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="13" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <v>46239</v>
@@ -708,7 +716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" ht="105" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <v>46239</v>
       </c>
@@ -721,66 +729,64 @@
       <c r="E14" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="2:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B15" s="3">
+        <v>46239</v>
+      </c>
+      <c r="C15">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>27</v>
+      </c>
       <c r="F15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="195" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <v>46239</v>
       </c>
       <c r="C16">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="195" x14ac:dyDescent="0.25">
-      <c r="B17" s="3">
-        <v>46239</v>
-      </c>
-      <c r="C17">
-        <v>60</v>
-      </c>
-      <c r="D17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F18" s="1"/>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G8" r:id="rId1" xr:uid="{2D576095-DD33-41E2-AE3D-624BFE4181D0}"/>
     <hyperlink ref="G9" r:id="rId2" xr:uid="{4C5458C7-3251-4B50-B993-29D9C5092585}"/>
     <hyperlink ref="G10" r:id="rId3" xr:uid="{37D06B73-17A9-4592-98F1-C038CB44CDA2}"/>
-    <hyperlink ref="G16" r:id="rId4" xr:uid="{AAFD389F-5339-488C-8F44-9A3F039DCFDD}"/>
-    <hyperlink ref="G17" r:id="rId5" display="https://open.spotify.com/episode/6Rljo1PtpUiz0N779Muyp0" xr:uid="{174DB1DB-772B-43EC-AFB0-0428427A70E8}"/>
+    <hyperlink ref="G15" r:id="rId4" xr:uid="{AAFD389F-5339-488C-8F44-9A3F039DCFDD}"/>
+    <hyperlink ref="G16" r:id="rId5" display="https://open.spotify.com/episode/6Rljo1PtpUiz0N779Muyp0" xr:uid="{174DB1DB-772B-43EC-AFB0-0428427A70E8}"/>
+    <hyperlink ref="G14" r:id="rId6" xr:uid="{13FFDDB7-34C5-44D7-8D29-9A080650B367}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Research Logs/Matt/Matt Baker - Week 4 Research Log.xlsx
+++ b/Research Logs/Matt/Matt Baker - Week 4 Research Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\BHB-Capstone\Research Logs\Matt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9108FB-8F29-4FB8-900A-DDA0996028AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29026C30-0461-46F7-9D3E-B375327BDCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2625" yWindow="1605" windowWidth="31305" windowHeight="16095" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
